--- a/logical function chapter 4.xlsx
+++ b/logical function chapter 4.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TANISHA\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/DB945125A59381F8/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F839B82F-0C3C-4A47-AE23-311204AB6CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{D07FBEAE-2A79-4C05-9115-FDA34BF10C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9348CCD1-D4F3-4A6E-8085-A5F2EF563DF8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AD277F7E-072A-4A66-A6C5-E50A3A834EE3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{AD277F7E-072A-4A66-A6C5-E50A3A834EE3}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="TARGET CHART" sheetId="1" r:id="rId1"/>
+    <sheet name="PROMOTION CHART" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,9 +36,243 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="68">
+  <si>
+    <t>EMP ID</t>
+  </si>
+  <si>
+    <t>EMP001</t>
+  </si>
+  <si>
+    <t>EMP002</t>
+  </si>
+  <si>
+    <t>EMP003</t>
+  </si>
+  <si>
+    <t>EMP004</t>
+  </si>
+  <si>
+    <t>EMP005</t>
+  </si>
+  <si>
+    <t>EMP006</t>
+  </si>
+  <si>
+    <t>EMP007</t>
+  </si>
+  <si>
+    <t>EMP008</t>
+  </si>
+  <si>
+    <t>EMP009</t>
+  </si>
+  <si>
+    <t>EMP010</t>
+  </si>
+  <si>
+    <t>EMP011</t>
+  </si>
+  <si>
+    <t>EMP012</t>
+  </si>
+  <si>
+    <t>Salesman</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Target Status</t>
+  </si>
+  <si>
+    <t>Incentive</t>
+  </si>
+  <si>
+    <t>Emp_1</t>
+  </si>
+  <si>
+    <t>Emp_2</t>
+  </si>
+  <si>
+    <t>Emp_3</t>
+  </si>
+  <si>
+    <t>Emp_4</t>
+  </si>
+  <si>
+    <t>Emp_5</t>
+  </si>
+  <si>
+    <t>Emp_6</t>
+  </si>
+  <si>
+    <t>Emp_7</t>
+  </si>
+  <si>
+    <t>Emp_8</t>
+  </si>
+  <si>
+    <t>Emp_9</t>
+  </si>
+  <si>
+    <t>Emp_10</t>
+  </si>
+  <si>
+    <t>Emp_11</t>
+  </si>
+  <si>
+    <t>Emp_12</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>Target Condition</t>
+  </si>
+  <si>
+    <t>Sales  Achieved</t>
+  </si>
+  <si>
+    <t>&gt;=50000</t>
+  </si>
+  <si>
+    <t>&lt;50000</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>incompleted</t>
+  </si>
+  <si>
+    <t>Incentive Calculation</t>
+  </si>
+  <si>
+    <t>75000&gt;</t>
+  </si>
+  <si>
+    <t>50000&gt;</t>
+  </si>
+  <si>
+    <t>Percentage</t>
+  </si>
+  <si>
+    <t>USE OF AND/OR</t>
+  </si>
+  <si>
+    <t>BOTH</t>
+  </si>
+  <si>
+    <t>FINANCE</t>
+  </si>
+  <si>
+    <t>5&gt;</t>
+  </si>
+  <si>
+    <t>PROMOTION</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>ANY ONE</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>EMPLOYEE_1</t>
+  </si>
+  <si>
+    <t>EMPLOYEE_2</t>
+  </si>
+  <si>
+    <t>EMPLOYEE_3</t>
+  </si>
+  <si>
+    <t>EMPLOYEE_4</t>
+  </si>
+  <si>
+    <t>EMPLOYEE_5</t>
+  </si>
+  <si>
+    <t>EMPLOYEE_6</t>
+  </si>
+  <si>
+    <t>EMPLOYEE_7</t>
+  </si>
+  <si>
+    <t>EMPLOYEE_8</t>
+  </si>
+  <si>
+    <t>EMPLOYEE_9</t>
+  </si>
+  <si>
+    <t>EMPLOYEE_10</t>
+  </si>
+  <si>
+    <t>EMPLOYEE_11</t>
+  </si>
+  <si>
+    <t>EMPLOYEE_12</t>
+  </si>
+  <si>
+    <t>WORKING YEARS</t>
+  </si>
+  <si>
+    <t>SALARY</t>
+  </si>
+  <si>
+    <t>DEPARTMENT</t>
+  </si>
+  <si>
+    <t>5&gt;=</t>
+  </si>
+  <si>
+    <t>OR PROMOTION</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_ &quot;₹&quot;\ * #,##0.00_ ;_ &quot;₹&quot;\ * \-#,##0.00_ ;_ &quot;₹&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -45,16 +280,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -62,14 +322,54 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -83,6 +383,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +706,788 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A25081-4B7D-44CC-A285-7703FE7EDE69}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2">
+        <v>72704</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <f>IF(D2&gt;=50000,"Completed","Incomplete")</f>
+        <v>Completed</v>
+      </c>
+      <c r="F2" s="2">
+        <f>IF(D2&gt;75000,D2*20%,IF(D2&gt;50000,D2*15%,D2*10%))</f>
+        <v>10905.6</v>
+      </c>
+      <c r="G2" cm="1">
+        <f t="array" ref="G2">_xlfn.IFS(D2&gt;75000,D2*20%,D2&gt;50000,D2*15%,D2&lt;=50000,D2*10%)</f>
+        <v>10905.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="2">
+        <v>44718</v>
+      </c>
+      <c r="E3" s="2" t="str">
+        <f t="shared" ref="E3:E13" si="0">IF(D3&gt;=50000,"Completed","Incomplete")</f>
+        <v>Incomplete</v>
+      </c>
+      <c r="F3" s="2">
+        <f t="shared" ref="F3:F13" si="1">IF(D3&gt;75000,D3*20%,IF(D3&gt;50000,D3*15%,D3*10%))</f>
+        <v>4471.8</v>
+      </c>
+      <c r="G3" cm="1">
+        <f t="array" ref="G3">_xlfn.IFS(D3&gt;75000,D3*20%,D3&gt;50000,D3*15%,D3&lt;=50000,D3*10%)</f>
+        <v>4471.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="2">
+        <v>35210</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Incomplete</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" si="1"/>
+        <v>3521</v>
+      </c>
+      <c r="G4" cm="1">
+        <f t="array" ref="G4">_xlfn.IFS(D4&gt;75000,D4*20%,D4&gt;50000,D4*15%,D4&lt;=50000,D4*10%)</f>
+        <v>3521</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="2">
+        <v>30681</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Incomplete</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="1"/>
+        <v>3068.1000000000004</v>
+      </c>
+      <c r="G5" cm="1">
+        <f t="array" ref="G5">_xlfn.IFS(D5&gt;75000,D5*20%,D5&gt;50000,D5*15%,D5&lt;=50000,D5*10%)</f>
+        <v>3068.1000000000004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2">
+        <v>47487</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Incomplete</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="1"/>
+        <v>4748.7</v>
+      </c>
+      <c r="G6" cm="1">
+        <f t="array" ref="G6">_xlfn.IFS(D6&gt;75000,D6*20%,D6&gt;50000,D6*15%,D6&lt;=50000,D6*10%)</f>
+        <v>4748.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="2">
+        <v>75613</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Completed</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" si="1"/>
+        <v>15122.6</v>
+      </c>
+      <c r="G7" cm="1">
+        <f t="array" ref="G7">_xlfn.IFS(D7&gt;75000,D7*20%,D7&gt;50000,D7*15%,D7&lt;=50000,D7*10%)</f>
+        <v>15122.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2">
+        <v>63671</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Completed</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="1"/>
+        <v>9550.65</v>
+      </c>
+      <c r="G8" cm="1">
+        <f t="array" ref="G8">_xlfn.IFS(D8&gt;75000,D8*20%,D8&gt;50000,D8*15%,D8&lt;=50000,D8*10%)</f>
+        <v>9550.65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="2">
+        <v>38966</v>
+      </c>
+      <c r="E9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Incomplete</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="1"/>
+        <v>3896.6000000000004</v>
+      </c>
+      <c r="G9" cm="1">
+        <f t="array" ref="G9">_xlfn.IFS(D9&gt;75000,D9*20%,D9&gt;50000,D9*15%,D9&lt;=50000,D9*10%)</f>
+        <v>3896.6000000000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="2">
+        <v>77052</v>
+      </c>
+      <c r="E10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Completed</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="1"/>
+        <v>15410.400000000001</v>
+      </c>
+      <c r="G10" cm="1">
+        <f t="array" ref="G10">_xlfn.IFS(D10&gt;75000,D10*20%,D10&gt;50000,D10*15%,D10&lt;=50000,D10*10%)</f>
+        <v>15410.400000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="2">
+        <v>86570</v>
+      </c>
+      <c r="E11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Completed</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" si="1"/>
+        <v>17314</v>
+      </c>
+      <c r="G11" cm="1">
+        <f t="array" ref="G11">_xlfn.IFS(D11&gt;75000,D11*20%,D11&gt;50000,D11*15%,D11&lt;=50000,D11*10%)</f>
+        <v>17314</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="2">
+        <v>30250</v>
+      </c>
+      <c r="E12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Incomplete</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="1"/>
+        <v>3025</v>
+      </c>
+      <c r="G12" cm="1">
+        <f t="array" ref="G12">_xlfn.IFS(D12&gt;75000,D12*20%,D12&gt;50000,D12*15%,D12&lt;=50000,D12*10%)</f>
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="2">
+        <v>71584</v>
+      </c>
+      <c r="E13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>Completed</v>
+      </c>
+      <c r="F13" s="2">
+        <f t="shared" si="1"/>
+        <v>10737.6</v>
+      </c>
+      <c r="G13" cm="1">
+        <f t="array" ref="G13">_xlfn.IFS(D13&gt;75000,D13*20%,D13&gt;50000,D13*15%,D13&lt;=50000,D13*10%)</f>
+        <v>10737.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" cm="1">
+        <f t="array" ref="G14">_xlfn.IFS(D14&gt;75000,D14*20%,D14&gt;50000,D14*15%,D14&lt;=50000,D14*10%)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B25" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="8"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B17:D17"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{403CDDF3-48C7-4BA2-8D3D-C8F60C94591F}">
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2" s="5">
+        <v>41954</v>
+      </c>
+      <c r="E2" s="2" t="str">
+        <f>IF(AND(B2="Finance",C2&gt;=5),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="F2" t="str">
+        <f>IF(OR(B2="Finance",C2&gt;=5),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2">
+        <v>4</v>
+      </c>
+      <c r="D3" s="5">
+        <v>49855</v>
+      </c>
+      <c r="E3" s="2" t="str">
+        <f t="shared" ref="E3:E13" si="0">IF(AND(B3="Finance",C3&gt;=5),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F13" si="1">IF(OR(B3="Finance",C3&gt;=5),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5">
+        <v>94210</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" s="5">
+        <v>74689</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>YES</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="1"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="2">
+        <v>6</v>
+      </c>
+      <c r="D6" s="5">
+        <v>90652</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="1"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>74820</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5">
+        <v>85206</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2">
+        <v>5</v>
+      </c>
+      <c r="D9" s="5">
+        <v>30924</v>
+      </c>
+      <c r="E9" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>YES</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="1"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="2">
+        <v>6</v>
+      </c>
+      <c r="D10" s="5">
+        <v>57737</v>
+      </c>
+      <c r="E10" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="1"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>36000</v>
+      </c>
+      <c r="E11" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3</v>
+      </c>
+      <c r="D12" s="5">
+        <v>96371</v>
+      </c>
+      <c r="E12" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="2">
+        <v>7</v>
+      </c>
+      <c r="D13" s="5">
+        <v>85028</v>
+      </c>
+      <c r="E13" s="2" t="str">
+        <f t="shared" si="0"/>
+        <v>NO</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="1"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B20" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B23" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B23:C23"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>